--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_movinterna_a_2024_maule.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_movinterna_a_2024_maule.xlsx
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 15:08</t>
+    <t xml:space="preserve">2026-09-24 01:57</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -576,13 +576,13 @@
         <v>30</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.26</v>
+        <v>0.28</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>-0.18</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="3">
@@ -599,13 +599,13 @@
         <v>30</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.29</v>
+        <v>0.35</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>-0.3</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="4">
@@ -622,13 +622,13 @@
         <v>30</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.25</v>
+        <v>0.27</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>-0.17</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="5">
@@ -645,13 +645,13 @@
         <v>30</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-0.18</v>
+        <v>-0.21</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.33</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="6">
@@ -668,13 +668,13 @@
         <v>30</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-0.3</v>
+        <v>-0.31</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="7">
@@ -944,13 +944,13 @@
         <v>30</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>0.23</v>
+        <v>0.29</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>-0.3</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="19">
@@ -967,13 +967,13 @@
         <v>30</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>-0.18</v>
+        <v>-0.17</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>-0.2</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="20">
@@ -990,13 +990,13 @@
         <v>30</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0.07</v>
+        <v>0.04</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>-0.34</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="21">
@@ -1013,13 +1013,13 @@
         <v>30</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>-0.2</v>
+        <v>-0.35</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.01</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="22">
@@ -1036,13 +1036,13 @@
         <v>30</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>-0.14</v>
+        <v>-0.31</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>0.1</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="23">
@@ -1059,13 +1059,13 @@
         <v>30</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>-0.14</v>
+        <v>-0.22</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>-0.01</v>
+        <v>0.07</v>
       </c>
     </row>
     <row r="24">
@@ -1105,13 +1105,13 @@
         <v>30</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>0.31</v>
+        <v>0.5</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>-0.09</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="26">
@@ -1131,10 +1131,10 @@
         <v>-0.13</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>-0.24</v>
+        <v>-0.25</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_movinterna_a_2024_maule.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_movinterna_a_2024_maule.xlsx
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:57</t>
+    <t xml:space="preserve">2026-10-01 23:17</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -153,7 +153,7 @@
     <t xml:space="preserve">plot_regional_correl_matriz_m_movinterna_a_2024_maule.png</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad territorial</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_movinterna_a_2024_maule.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_movinterna_a_2024_maule.xlsx
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:17</t>
+    <t xml:space="preserve">2026-10-05 20:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
